--- a/docs/keyword-map.xlsx
+++ b/docs/keyword-map.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/b530eccc-Keyword_Canada.xlsx</t>
+          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/d56f9b2b-Keyword_Canada.xlsx</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -4742,7 +4742,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iptv android</t>
+          <t>iplaytv apple tv</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>/iptv-android-tv/</t>
+          <t>/iplaytv/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4773,21 +4773,17 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>manual override</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iptv android tv</t>
+          <t>iptv android</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4818,7 +4814,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -4828,7 +4828,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iptv google tv</t>
+          <t>iptv android tv</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4869,7 +4869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iptv nvidia shield</t>
+          <t>iptv google tv</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4910,7 +4910,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mi box iptv</t>
+          <t>iptv nvidia shield</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4951,7 +4951,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nvidia shield iptv</t>
+          <t>mi box iptv</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4992,7 +4992,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>smart iptv android tv</t>
+          <t>nvidia shield iptv</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5033,7 +5033,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>xiaomi iptv</t>
+          <t>smart iptv android tv</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>xiaomi iptv box</t>
+          <t>xiaomi iptv</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -5115,7 +5115,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iptv apple tv 4k</t>
+          <t>xiaomi iptv box</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>/iptv-apple-tv/</t>
+          <t>/iptv-android-tv/</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5146,11 +5146,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -5160,15 +5156,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iptv on apple tv 4k</t>
+          <t>iptv apple tv</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5191,17 +5187,21 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>manual override</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>iptv smarters apple tv</t>
+          <t>iptv apple tv 4k</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5242,7 +5242,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>iptv smasters pro apple tv</t>
+          <t>iptv on apple tv 4k</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -5283,7 +5283,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iptvx apple tv</t>
+          <t>iptv smarters apple tv</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -5324,25 +5324,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iptvapp</t>
+          <t>iptv smasters pro apple tv</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>/iptv-apps/</t>
+          <t>/iptv-apple-tv/</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5355,11 +5355,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -5369,11 +5365,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>android iptv player</t>
+          <t>iptvx apple tv</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5382,12 +5378,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>/iptv-apps/</t>
+          <t>/iptv-apple-tv/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5410,11 +5406,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ip tv stream player</t>
+          <t>iptvapp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5441,7 +5437,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -5451,7 +5451,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iptv stream player</t>
+          <t>android iptv player</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5492,7 +5492,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>myiptv player</t>
+          <t>ip tv stream player</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5526,14 +5526,14 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>smart iptv player</t>
+          <t>iptv stream player</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5574,11 +5574,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>best iptv app</t>
+          <t>myiptv player</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5608,18 +5608,18 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>best iptv apps</t>
+          <t>smart iptv player</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5656,11 +5656,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iptv media player</t>
+          <t>best iptv app</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5697,11 +5697,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iptv stream player pro</t>
+          <t>best iptv apps</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5731,14 +5731,14 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>live tv player</t>
+          <t>iptv media player</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -5772,18 +5772,18 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>iptv box</t>
+          <t>iptv stream player pro</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>8400</v>
+        <v>50</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5792,12 +5792,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>/iptv-box/</t>
+          <t>/iptv-apps/</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5810,25 +5810,21 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ip tv box</t>
+          <t>live tv player</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5837,12 +5833,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>/iptv-box/</t>
+          <t>/iptv-apps/</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5858,18 +5854,18 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iptv with box</t>
+          <t>iptv box</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2400</v>
+        <v>8400</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5896,7 +5892,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -5906,11 +5906,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>amazon iptv box</t>
+          <t>ip tv box</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5947,11 +5947,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>best android box for iptv</t>
+          <t>iptv with box</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>best android tv box for iptv</t>
+          <t>amazon iptv box</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -6029,7 +6029,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>best iptv box</t>
+          <t>best android box for iptv</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -6070,7 +6070,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>box android iptv</t>
+          <t>best android tv box for iptv</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -6111,7 +6111,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>box iptv</t>
+          <t>best iptv box</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -6152,7 +6152,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>box iptv 4k</t>
+          <t>box android iptv</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -6193,7 +6193,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ip box tv</t>
+          <t>box iptv</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -6234,7 +6234,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iptv android tv box</t>
+          <t>box iptv 4k</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -6275,7 +6275,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iptv box amazon</t>
+          <t>ip box tv</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -6316,7 +6316,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iptv box android</t>
+          <t>iptv android tv box</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -6357,7 +6357,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iptv box near me</t>
+          <t>iptv box amazon</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -6398,7 +6398,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iptv box price</t>
+          <t>iptv box android</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -6439,7 +6439,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>onn tv box</t>
+          <t>iptv box near me</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -6480,11 +6480,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>box tv iptv</t>
+          <t>iptv box price</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6514,18 +6514,18 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>buzztv xrs 4900</t>
+          <t>onn tv box</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>buzztv xrs4500</t>
+          <t>box tv iptv</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -6596,14 +6596,14 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>dlta 4k</t>
+          <t>buzztv xrs 4900</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -6637,14 +6637,14 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>dlta 4k iptv</t>
+          <t>buzztv xrs4500</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -6678,14 +6678,14 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>dreamlink box</t>
+          <t>dlta 4k</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -6726,7 +6726,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>global tv box</t>
+          <t>dlta 4k iptv</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -6767,7 +6767,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iptv smart box</t>
+          <t>dreamlink box</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -6801,14 +6801,14 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>meilleur box iptv</t>
+          <t>global tv box</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -6842,14 +6842,14 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tv ip box</t>
+          <t>iptv smart box</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -6883,18 +6883,18 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>fast iptv</t>
+          <t>meilleur box iptv</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6903,17 +6903,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>/iptv-buffering-fix/</t>
+          <t>/iptv-box/</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6921,11 +6921,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -6935,7 +6931,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iptv rapid</t>
+          <t>tv ip box</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6948,17 +6944,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>/iptv-buffering-fix/</t>
+          <t>/iptv-box/</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6969,18 +6965,18 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iptv sans coupure</t>
+          <t>fast iptv</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7007,7 +7003,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7017,7 +7017,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iptv stable</t>
+          <t>iptv rapid</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -7058,7 +7058,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rapidiptv</t>
+          <t>iptv sans coupure</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -7099,7 +7099,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>chromecast iptv</t>
+          <t>iptv stable</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -7112,17 +7112,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>/iptv-chromecast/</t>
+          <t>/iptv-buffering-fix/</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7130,11 +7130,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7144,7 +7140,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>gse iptv chromecast</t>
+          <t>rapidiptv</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -7152,22 +7148,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>/iptv-chromecast/</t>
+          <t>/iptv-buffering-fix/</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7185,7 +7181,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>iptv google chromecast</t>
+          <t>chromecast iptv</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -7193,7 +7189,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7216,7 +7212,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7226,7 +7226,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>iptv smarters chromecast</t>
+          <t>gse iptv chromecast</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -7267,7 +7267,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>smarters player lite chromecast</t>
+          <t>iptv chromecast</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7301,27 +7301,27 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>manual override</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iptv set top box</t>
+          <t>iptv google chromecast</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>/iptv-devices/</t>
+          <t>/iptv-chromecast/</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7339,11 +7339,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7353,20 +7349,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>set top box iptv</t>
+          <t>iptv smarters chromecast</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>/iptv-devices/</t>
+          <t>/iptv-chromecast/</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7394,7 +7390,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>iptv device</t>
+          <t>smarters player lite chromecast</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -7402,12 +7398,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>/iptv-devices/</t>
+          <t>/iptv-chromecast/</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7435,11 +7431,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iptv receiver</t>
+          <t>iptv set top box</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -7466,7 +7462,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7476,11 +7476,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>iptv firestick</t>
+          <t>set top box iptv</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>590</v>
+        <v>500</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>/iptv-firestick/</t>
+          <t>/iptv-devices/</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7507,11 +7507,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7521,11 +7517,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>best iptv for firestick</t>
+          <t>iptv device</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -7534,7 +7530,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>/iptv-firestick/</t>
+          <t>/iptv-devices/</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7562,11 +7558,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>fire tv iptv</t>
+          <t>iptv receiver</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -7575,7 +7571,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>/iptv-firestick/</t>
+          <t>/iptv-devices/</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7603,11 +7599,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>fire tv stick iptv</t>
+          <t>iptv firestick</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7634,7 +7630,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -7644,7 +7644,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ip tv amazon</t>
+          <t>best iptv for firestick</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -7685,7 +7685,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>iptv amazon</t>
+          <t>fire tv iptv</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -7726,7 +7726,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>iptv fire stick</t>
+          <t>fire tv stick iptv</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -7767,7 +7767,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>iptv for firestick</t>
+          <t>ip tv amazon</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -7808,7 +7808,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>iptv stick</t>
+          <t>iptv amazon</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -7849,11 +7849,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>fire stick iptv</t>
+          <t>iptv fire stick</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7890,11 +7890,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>iptv amazon stick</t>
+          <t>iptv for firestick</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7931,15 +7931,15 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>iptv amazon tv</t>
+          <t>iptv stick</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7965,22 +7965,22 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>iptv sur fire stick</t>
+          <t>fire stick iptv</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8013,7 +8013,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>smart iptv firestick</t>
+          <t>iptv amazon stick</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8054,11 +8054,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>iptv for beginners</t>
+          <t>iptv amazon tv</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -8067,17 +8067,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>/iptv-guides/</t>
+          <t>/iptv-firestick/</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>hub</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8085,44 +8085,40 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>iptv world</t>
+          <t>iptv sur fire stick</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>880</v>
+        <v>50</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>/iptv-international/</t>
+          <t>/iptv-firestick/</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>International communities</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>F community hub</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8130,11 +8126,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8144,7 +8136,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>euro iptv</t>
+          <t>smart iptv firestick</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -8152,22 +8144,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>/iptv-international/</t>
+          <t>/iptv-firestick/</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>International communities</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>F community hub</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8185,30 +8177,30 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>euroiptv</t>
+          <t>iptv for beginners</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>/iptv-international/</t>
+          <t>/iptv-guides/</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>International communities</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>F community hub</t>
+          <t>hub</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8216,7 +8208,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8226,11 +8222,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>iptv global</t>
+          <t>iptv world</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>50</v>
+        <v>880</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -8257,7 +8253,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8267,7 +8267,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>worldwide iptv</t>
+          <t>euro iptv</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -8308,30 +8308,30 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>iptv iphone</t>
+          <t>euroiptv</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>/iptv-iphone/</t>
+          <t>/iptv-international/</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>International communities</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>F community hub</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8339,11 +8339,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8353,11 +8349,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>iptvx</t>
+          <t>iptv global</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -8366,17 +8362,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>/iptv-iphone/</t>
+          <t>/iptv-international/</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>International communities</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>F community hub</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -8394,7 +8390,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>atlas pro ontv iphone</t>
+          <t>worldwide iptv</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -8402,22 +8398,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>/iptv-iphone/</t>
+          <t>/iptv-international/</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>International communities</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>F community hub</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8435,15 +8431,15 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>gseiptv</t>
+          <t>iptv iphone</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8466,7 +8462,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I188" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8476,11 +8476,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>iptv mobile</t>
+          <t>iptvx</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>iptv smasters iphone</t>
+          <t>atlas pro ontv iphone</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -8558,11 +8558,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>iptv légal</t>
+          <t>gseiptv</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -8571,29 +8571,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>/iptv-legal-canada/</t>
+          <t>/iptv-iphone/</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>fr-CA</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8603,7 +8599,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>iptv bloqué</t>
+          <t>iptv mobile</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -8611,34 +8607,30 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>/iptv-ne-fonctionne-plus/</t>
+          <t>/iptv-iphone/</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>fr-CA</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8648,7 +8640,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>iptv ne fonctionne plus</t>
+          <t>iptv smasters iphone</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -8661,22 +8653,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>/iptv-ne-fonctionne-plus/</t>
+          <t>/iptv-iphone/</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
@@ -8689,11 +8681,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>iptv near me</t>
+          <t>iptv légal</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8702,22 +8694,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>/iptv-near-me/</t>
+          <t>/iptv-legal-canada/</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>E geo hub</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8734,30 +8726,30 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>iptv areas</t>
+          <t>iptv lifetime</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>720</v>
+        <v>50</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>/iptv-near-me/</t>
+          <t>/iptv-lifetime/</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>E geo hub</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8765,7 +8757,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8775,11 +8771,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>best iptv near me</t>
+          <t>lifetime iptv</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>590</v>
+        <v>50</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8788,17 +8784,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>/iptv-near-me/</t>
+          <t>/iptv-lifetime/</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>E geo hub</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8816,38 +8812,42 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iptv 4k near me</t>
+          <t>iptv bloqué</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>590</v>
+        <v>50</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>/iptv-near-me/</t>
+          <t>/iptv-ne-fonctionne-plus/</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>E geo hub</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>en-CA</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
+          <t>fr-CA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8857,35 +8857,35 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>iptv service near me</t>
+          <t>iptv ne fonctionne plus</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>/iptv-near-me/</t>
+          <t>/iptv-ne-fonctionne-plus/</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>E geo hub</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
@@ -8898,11 +8898,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>local iptv</t>
+          <t>iptv near me</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>50</v>
+        <v>1900</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8929,7 +8929,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -8939,11 +8943,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>starlink iptv</t>
+          <t>iptv areas</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>50</v>
+        <v>720</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8980,11 +8984,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>iptv pas cher</t>
+          <t>best iptv near me</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>50</v>
+        <v>590</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -8993,29 +8997,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>/iptv-pas-cher/</t>
+          <t>/iptv-near-me/</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>E geo hub</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>fr-CA</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9025,11 +9025,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>iptv prix</t>
+          <t>iptv 4k near me</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>50</v>
+        <v>590</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -9038,22 +9038,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>/iptv-pas-cher/</t>
+          <t>/iptv-near-me/</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>E geo hub</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
@@ -9066,11 +9066,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>prix iptv</t>
+          <t>iptv service near me</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -9079,22 +9079,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>/iptv-pas-cher/</t>
+          <t>/iptv-near-me/</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>E geo hub</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
@@ -9107,11 +9107,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ip tv subscription</t>
+          <t>local iptv</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -9120,17 +9120,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>/iptv-plans-canada/</t>
+          <t>/iptv-near-me/</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Core / conversion</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>A subscription landing</t>
+          <t>E geo hub</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -9138,11 +9138,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9152,30 +9148,30 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>iptv subscribe</t>
+          <t>starlink iptv</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>/iptv-plans-canada/</t>
+          <t>/iptv-near-me/</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Core / conversion</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>A subscription landing</t>
+          <t>E geo hub</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9193,11 +9189,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>iptv subscription</t>
+          <t>iptv pas cher</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1600</v>
+        <v>50</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -9206,25 +9202,29 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>/iptv-plans-canada/</t>
+          <t>/iptv-pas-cher/</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Core / conversion</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>A subscription landing</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>en-CA</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
+          <t>fr-CA</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9234,11 +9234,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>iptv subscription canada</t>
+          <t>iptv prix</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1300</v>
+        <v>50</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -9247,22 +9247,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>/iptv-plans-canada/</t>
+          <t>/iptv-pas-cher/</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Core / conversion</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>A subscription landing</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
@@ -9275,11 +9275,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>best iptv subscription</t>
+          <t>prix iptv</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -9288,22 +9288,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>/iptv-plans-canada/</t>
+          <t>/iptv-pas-cher/</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Core / conversion</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>A subscription landing</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
@@ -9316,11 +9316,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>buy iptv</t>
+          <t>ip tv subscription</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -9347,7 +9347,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9357,11 +9361,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>iptv plans</t>
+          <t>iptv subscribe</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -9398,11 +9402,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>iptv sub</t>
+          <t>iptv subscription</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -9439,11 +9443,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>buy iptv online</t>
+          <t>iptv subscription canada</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>50</v>
+        <v>1300</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -9480,11 +9484,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>buy iptv subscription</t>
+          <t>best iptv subscription</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -9521,11 +9525,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>iptv packages</t>
+          <t>buy iptv</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -9562,11 +9566,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>iptv premium subscription</t>
+          <t>iptv plans</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -9603,11 +9607,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>iptv subscription ebay</t>
+          <t>iptv sub</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -9637,18 +9641,18 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>cheap iptv</t>
+          <t>buy iptv online</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -9657,17 +9661,17 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-plans-canada/</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Core / conversion</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>A subscription landing</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9675,11 +9679,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9689,11 +9689,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>iptv cost</t>
+          <t>buy iptv subscription</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -9702,17 +9702,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-plans-canada/</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Core / conversion</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>A subscription landing</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9730,11 +9730,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>iptv deals</t>
+          <t>iptv packages</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -9743,17 +9743,17 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-plans-canada/</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Core / conversion</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>A subscription landing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9771,11 +9771,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>iptv price</t>
+          <t>iptv premium subscription</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -9784,17 +9784,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-plans-canada/</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Core / conversion</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>A subscription landing</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9812,7 +9812,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>iptv lifetime</t>
+          <t>iptv subscription ebay</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -9825,17 +9825,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-plans-canada/</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Core / conversion</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>A subscription landing</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9853,11 +9853,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>iptv promo</t>
+          <t>cheap iptv</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -9884,7 +9884,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I222" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -9894,11 +9898,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>iptv promotions</t>
+          <t>iptv cost</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -9935,11 +9939,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>lifetime iptv</t>
+          <t>iptv deals</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -9969,18 +9973,18 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>iptv providers</t>
+          <t>iptv price</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -9989,7 +9993,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>/iptv-providers/</t>
+          <t>/iptv-price/</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -9999,7 +10003,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>B comparison / best-of</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -10007,11 +10011,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10021,11 +10021,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>provider iptv</t>
+          <t>iptv promo</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>/iptv-providers/</t>
+          <t>/iptv-price/</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>B comparison / best-of</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -10062,11 +10062,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>iptv providers canada</t>
+          <t>iptv promotions</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>/iptv-providers/</t>
+          <t>/iptv-price/</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>B comparison / best-of</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -10103,11 +10103,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>iptv resellers</t>
+          <t>iptv providers</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -10134,7 +10134,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10144,11 +10148,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>iptv service</t>
+          <t>provider iptv</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -10185,7 +10189,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>iptv supplier</t>
+          <t>iptv providers canada</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -10226,11 +10230,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>best iptv resell</t>
+          <t>iptv resellers</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>590</v>
+        <v>1200</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -10267,11 +10271,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>best iptv service provider</t>
+          <t>iptv service</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -10308,11 +10312,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>iptv service provider</t>
+          <t>iptv supplier</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -10349,11 +10353,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>top iptv</t>
+          <t>best iptv resell</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -10390,7 +10394,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>top iptv providers</t>
+          <t>best iptv service provider</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -10431,11 +10435,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>best iptv providers</t>
+          <t>iptv service provider</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -10472,11 +10476,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>iptv providers in canada</t>
+          <t>top iptv</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -10513,11 +10517,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>iptv top</t>
+          <t>top iptv providers</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -10554,11 +10558,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>service iptv</t>
+          <t>best iptv providers</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>320</v>
+        <v>490</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -10595,11 +10599,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>iptv provider canada</t>
+          <t>iptv providers in canada</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>260</v>
+        <v>490</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -10636,11 +10640,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>iptvresale</t>
+          <t>iptv top</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -10677,11 +10681,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>canal iptv</t>
+          <t>service iptv</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -10690,29 +10694,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>/iptv-quebec/</t>
+          <t>/iptv-providers/</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>B comparison / best-of</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>fr-CA</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10722,20 +10722,20 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>iptv reddit</t>
+          <t>iptv provider canada</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>5000</v>
+        <v>260</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>/iptv-reddit/</t>
+          <t>/iptv-providers/</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>B comparison / best-of</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -10753,11 +10753,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10767,20 +10763,20 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>reddit iptv</t>
+          <t>iptvresale</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>590</v>
+        <v>50</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>/iptv-reddit/</t>
+          <t>/iptv-providers/</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -10790,7 +10786,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>B comparison / best-of</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -10808,11 +10804,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>best iptv provider</t>
+          <t>canal iptv</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -10821,25 +10817,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>/iptv-reddit/</t>
+          <t>/iptv-quebec/</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>en-CA</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr"/>
+          <t>fr-CA</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10849,15 +10849,15 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>best iptv provider reddit</t>
+          <t>iptv reddit</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10880,7 +10880,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -10890,15 +10894,15 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>best iptv reddit</t>
+          <t>reddit iptv</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10931,7 +10935,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>best iptv service reddit</t>
+          <t>best iptv provider</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -10972,7 +10976,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>iptv firestick reddit</t>
+          <t>best iptv provider reddit</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -11013,7 +11017,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>iptv providers reddit</t>
+          <t>best iptv reddit</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -11054,7 +11058,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>iptv services reddit</t>
+          <t>best iptv service reddit</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -11095,7 +11099,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>iptv subscription reddit</t>
+          <t>iptv firestick reddit</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -11136,7 +11140,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>iptvforum</t>
+          <t>iptv providers reddit</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -11144,7 +11148,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11177,7 +11181,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>reddit best iptv</t>
+          <t>iptv services reddit</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -11185,7 +11189,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -11218,7 +11222,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>tivimate reddit</t>
+          <t>iptv subscription reddit</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -11226,7 +11230,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -11259,15 +11263,15 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>firestick iptv reddit</t>
+          <t>iptvforum</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -11300,15 +11304,15 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>iptv on firestick reddit</t>
+          <t>reddit best iptv</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11341,11 +11345,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>iptv smasters reddit</t>
+          <t>tivimate reddit</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -11382,7 +11386,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>iptv smasters subscription reddit</t>
+          <t>firestick iptv reddit</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -11423,7 +11427,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>iptv trustpilot</t>
+          <t>iptv on firestick reddit</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -11431,7 +11435,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -11464,7 +11468,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kemo iptv reddit</t>
+          <t>iptv smasters reddit</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -11472,7 +11476,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11505,7 +11509,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>reddit tivimate</t>
+          <t>iptv smasters subscription reddit</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -11513,7 +11517,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -11546,7 +11550,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>trustpilot iptv</t>
+          <t>iptv trustpilot</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -11587,7 +11591,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>xtreme hd iptv reddit</t>
+          <t>kemo iptv reddit</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -11628,20 +11632,20 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>iptv canada reviews</t>
+          <t>reddit tivimate</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>590</v>
+        <v>50</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>/iptv-reviews/</t>
+          <t>/iptv-reddit/</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11659,11 +11663,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -11673,20 +11673,20 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>iptv reviews</t>
+          <t>trustpilot iptv</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>490</v>
+        <v>50</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>/iptv-reviews/</t>
+          <t>/iptv-reddit/</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11714,30 +11714,30 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>iptv on roku tv</t>
+          <t>xtreme hd iptv reddit</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>/iptv-roku/</t>
+          <t>/iptv-reddit/</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -11745,11 +11745,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -11759,30 +11755,30 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>iptv roku</t>
+          <t>iptv canada reviews</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>/iptv-roku/</t>
+          <t>/iptv-reviews/</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -11790,7 +11786,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -11800,30 +11800,30 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>iptv roku tv</t>
+          <t>iptv reviews</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>/iptv-roku/</t>
+          <t>/iptv-reviews/</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>roku tv iptv</t>
+          <t>iptv on roku tv</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -11872,7 +11872,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I270" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -11882,11 +11886,11 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>iptv smasters on roku tv</t>
+          <t>iptv roku</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -11923,11 +11927,11 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>iptv smasters pro roku</t>
+          <t>iptv roku tv</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -11964,11 +11968,11 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>roku express iptv</t>
+          <t>roku tv iptv</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -12005,11 +12009,11 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>iptv for samsung tv</t>
+          <t>iptv smasters on roku tv</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -12018,7 +12022,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>/iptv-samsung-tv/</t>
+          <t>/iptv-roku/</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -12036,11 +12040,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -12050,11 +12050,11 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>iptv samsung tv</t>
+          <t>iptv smasters pro roku</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>/iptv-samsung-tv/</t>
+          <t>/iptv-roku/</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -12091,7 +12091,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ip tv samsung</t>
+          <t>roku express iptv</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>/iptv-samsung-tv/</t>
+          <t>/iptv-roku/</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -12132,11 +12132,11 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>iptv server</t>
+          <t>iptv for samsung tv</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -12145,17 +12145,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>/iptv-server/</t>
+          <t>/iptv-samsung-tv/</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -12177,7 +12177,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>iptv servers</t>
+          <t>iptv samsung tv</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -12190,17 +12190,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>/iptv-server/</t>
+          <t>/iptv-samsung-tv/</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -12218,11 +12218,11 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>iptv control</t>
+          <t>ip tv samsung</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>490</v>
+        <v>50</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -12231,17 +12231,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>/iptv-server/</t>
+          <t>/iptv-samsung-tv/</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -12259,15 +12259,15 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>iptv connect</t>
+          <t>iptv server</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>50</v>
+        <v>1300</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -12290,7 +12290,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I280" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -12300,15 +12304,15 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>iptv connect pro</t>
+          <t>iptv servers</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -12341,15 +12345,15 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>iptv line</t>
+          <t>iptv control</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -12382,30 +12386,30 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>iptv downloader</t>
+          <t>iptv connect</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-download/</t>
+          <t>/iptv-server/</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -12413,11 +12417,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -12427,30 +12427,30 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>iptv smarters downloader</t>
+          <t>iptv connect pro</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-download/</t>
+          <t>/iptv-server/</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -12468,11 +12468,11 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>iptv smarters pro android</t>
+          <t>iptv line</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -12481,17 +12481,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-download/</t>
+          <t>/iptv-server/</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>iptv smarters pro free</t>
+          <t>iptv downloader</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -12540,7 +12540,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I286" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -12550,7 +12554,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>smarters iptv pro</t>
+          <t>iptv smarters downloader</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -12558,7 +12562,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -12591,7 +12595,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>smarters pro iptv</t>
+          <t>iptv smarters pro android</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -12632,15 +12636,15 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ip smarter pro</t>
+          <t>iptv smarters pro free</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -12673,11 +12677,11 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ip smarters pro</t>
+          <t>smarters iptv pro</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -12714,15 +12718,15 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>iptv customer service</t>
+          <t>smarters pro iptv</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -12755,7 +12759,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>iptv smarters android</t>
+          <t>ip smarter pro</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -12763,7 +12767,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -12796,7 +12800,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>iptv smarters com</t>
+          <t>ip smarters pro</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -12837,7 +12841,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>iptv smarters customer service</t>
+          <t>iptv customer service</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -12878,7 +12882,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>iptv smasters free</t>
+          <t>iptv smarters android</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -12919,7 +12923,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>iptv smasters google play</t>
+          <t>iptv smarters com</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -12927,7 +12931,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -12960,7 +12964,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>iptv smasters m3u</t>
+          <t>iptv smarters customer service</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -13001,7 +13005,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>iptv smasters player android</t>
+          <t>iptv smasters free</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -13042,7 +13046,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>iptv smasters premium</t>
+          <t>iptv smasters google play</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -13050,7 +13054,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -13083,7 +13087,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>iptv smasters pro com</t>
+          <t>iptv smasters m3u</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -13091,7 +13095,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -13124,7 +13128,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>iptv smasters pro introuvable google play</t>
+          <t>iptv smasters player android</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -13165,7 +13169,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>iptv smasters pro live</t>
+          <t>iptv smasters premium</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -13206,7 +13210,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>iptv smasters pro m3u</t>
+          <t>iptv smasters pro com</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -13214,7 +13218,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -13247,7 +13251,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>iptv smasters pro price</t>
+          <t>iptv smasters pro introuvable google play</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -13255,7 +13259,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -13288,7 +13292,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>m3u downloader online</t>
+          <t>iptv smasters pro live</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -13296,7 +13300,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -13329,7 +13333,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>smart iptv downloader</t>
+          <t>iptv smasters pro m3u</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -13370,11 +13374,11 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>iptv smarters pro firestick</t>
+          <t>iptv smasters pro price</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -13383,7 +13387,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-firestick/</t>
+          <t>/iptv-smarters-pro-download/</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -13401,11 +13405,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -13415,7 +13415,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>iptv smasters android tv</t>
+          <t>m3u downloader online</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-firestick/</t>
+          <t>/iptv-smarters-pro-download/</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -13456,7 +13456,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>iptv smasters fire stick</t>
+          <t>smart iptv downloader</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-firestick/</t>
+          <t>/iptv-smarters-pro-download/</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -13497,11 +13497,11 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>iptv smasters firestick</t>
+          <t>iptv smarters pro firestick</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -13528,7 +13528,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I310" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -13538,7 +13542,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>iptv smasters for firestick</t>
+          <t>iptv smasters android tv</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -13546,7 +13550,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -13579,7 +13583,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>iptv smasters on firestick</t>
+          <t>iptv smasters fire stick</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -13587,7 +13591,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -13620,7 +13624,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>iptv smasters pro android tv</t>
+          <t>iptv smasters firestick</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -13628,7 +13632,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -13661,7 +13665,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>iptv smasters pro downloader</t>
+          <t>iptv smasters for firestick</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -13669,7 +13673,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -13702,7 +13706,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>iptv smasters pro fire stick</t>
+          <t>iptv smasters on firestick</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -13710,7 +13714,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -13743,7 +13747,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>smarters iptv firestick</t>
+          <t>iptv smasters pro android tv</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -13751,7 +13755,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -13784,7 +13788,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>smarters player lite firestick</t>
+          <t>iptv smasters pro downloader</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -13792,7 +13796,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -13825,7 +13829,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>smarters pro firestick</t>
+          <t>iptv smasters pro fire stick</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -13833,7 +13837,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -13866,7 +13870,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>xciptv firestick</t>
+          <t>smarters iptv firestick</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -13907,7 +13911,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>iptv smasters pro ne fonctionne pas sur tv samsung</t>
+          <t>smarters player lite firestick</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -13915,34 +13919,30 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-francais/</t>
+          <t>/iptv-smarters-pro-firestick/</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>fr-CA</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -13952,7 +13952,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>smarters player lite sur tv samsung</t>
+          <t>smarters pro firestick</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -13960,27 +13960,27 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-francais/</t>
+          <t>/iptv-smarters-pro-firestick/</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
@@ -13993,7 +13993,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>smasters player lite télécharger</t>
+          <t>xciptv firestick</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -14001,27 +14001,27 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-francais/</t>
+          <t>/iptv-smarters-pro-firestick/</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
@@ -14034,11 +14034,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>iptv pc</t>
+          <t>iptv smasters pro ne fonctionne pas sur tv samsung</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -14047,22 +14047,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-pc-mac/</t>
+          <t>/iptv-smarters-pro-francais/</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14079,11 +14079,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>iptv player pc</t>
+          <t>smarters player lite sur tv samsung</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -14092,22 +14092,22 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-pc-mac/</t>
+          <t>/iptv-smarters-pro-francais/</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
@@ -14120,11 +14120,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>iptv smarters pro pc</t>
+          <t>smasters player lite télécharger</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -14133,22 +14133,22 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-pc-mac/</t>
+          <t>/iptv-smarters-pro-francais/</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
@@ -14161,11 +14161,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ip tv pc</t>
+          <t>iptv pc</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -14192,7 +14192,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I326" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -14202,11 +14206,11 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>iptv laptop</t>
+          <t>iptv player pc</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -14243,11 +14247,11 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>iptv macbook</t>
+          <t>iptv smarters pro pc</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -14284,7 +14288,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>iptv smarter pc</t>
+          <t>ip tv pc</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -14325,7 +14329,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>iptv smasters for pc</t>
+          <t>iptv laptop</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -14366,7 +14370,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>iptv smasters mac</t>
+          <t>iptv macbook</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -14407,7 +14411,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>iptv smasters pc</t>
+          <t>iptv smarter pc</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -14448,7 +14452,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>iptv smasters pour pc</t>
+          <t>iptv smasters for pc</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -14489,7 +14493,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>iptv smasters pro for pc</t>
+          <t>iptv smasters mac</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -14530,7 +14534,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>iptv smasters pro mac</t>
+          <t>iptv smasters pc</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -14571,7 +14575,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>iptv smasters pro macbook</t>
+          <t>iptv smasters pour pc</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -14612,7 +14616,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>iptv smasters pro sur pc</t>
+          <t>iptv smasters pro for pc</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -14653,7 +14657,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>m3u player pc</t>
+          <t>iptv smasters pro mac</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -14694,7 +14698,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>mac iptv</t>
+          <t>iptv smasters pro macbook</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -14735,7 +14739,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>smart iptv mac</t>
+          <t>iptv smasters pro sur pc</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -14776,7 +14780,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>smart iptv pc</t>
+          <t>m3u player pc</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -14817,7 +14821,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>smarters pro pc</t>
+          <t>mac iptv</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -14858,7 +14862,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>strymtv for pc</t>
+          <t>smart iptv mac</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -14866,7 +14870,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -14899,7 +14903,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>iptv for lg webos</t>
+          <t>smart iptv pc</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -14912,7 +14916,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-samsung-lg/</t>
+          <t>/iptv-smarters-pro-pc-mac/</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -14930,11 +14934,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -14944,7 +14944,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>iptv samsung tizen</t>
+          <t>smarters pro pc</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-samsung-lg/</t>
+          <t>/iptv-smarters-pro-pc-mac/</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -14985,7 +14985,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>iptv smasters lg</t>
+          <t>strymtv for pc</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -14993,12 +14993,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro-samsung-lg/</t>
+          <t>/iptv-smarters-pro-pc-mac/</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>iptv smasters lg tv</t>
+          <t>iptv for lg webos</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -15057,7 +15057,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I347" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -15067,7 +15071,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>iptv smasters player samsung</t>
+          <t>iptv samsung tizen</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -15108,7 +15112,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>iptv smasters pro lg</t>
+          <t>iptv smasters lg</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -15149,7 +15153,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>iptv smasters pro samsung tv</t>
+          <t>iptv smasters lg tv</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -15190,7 +15194,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>iptv smasters pro smart tv</t>
+          <t>iptv smasters player samsung</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -15231,7 +15235,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>iptv smasters pro tv</t>
+          <t>iptv smasters pro lg</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -15239,7 +15243,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15272,7 +15276,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>iptv smasters samsung</t>
+          <t>iptv smasters pro samsung tv</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -15313,7 +15317,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>iptv smasters samsung tv</t>
+          <t>iptv smasters pro smart tv</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -15354,7 +15358,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>iptv smasters smart tv</t>
+          <t>iptv smasters pro tv</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -15362,7 +15366,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -15395,7 +15399,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>iptv smasters tv</t>
+          <t>iptv smasters samsung</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -15403,7 +15407,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -15436,7 +15440,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>iptv tizen</t>
+          <t>iptv smasters samsung tv</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -15477,7 +15481,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>samsung iptv smarters</t>
+          <t>iptv smasters smart tv</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -15518,7 +15522,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>samsung tizen iptv</t>
+          <t>iptv smasters tv</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -15526,7 +15530,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -15559,7 +15563,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>smarter player pro</t>
+          <t>iptv tizen</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -15567,7 +15571,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -15600,7 +15604,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>smarters lite</t>
+          <t>samsung iptv smarters</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -15608,7 +15612,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -15641,7 +15645,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>smarters player lite samsung tv</t>
+          <t>samsung tizen iptv</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -15682,7 +15686,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>smarters player lite tv</t>
+          <t>smarter player pro</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -15690,7 +15694,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -15723,7 +15727,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>smarters player pro</t>
+          <t>smarters lite</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -15764,7 +15768,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>smarters player tv</t>
+          <t>smarters player lite samsung tv</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -15772,7 +15776,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -15805,7 +15809,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>smarters pro lite</t>
+          <t>smarters player lite tv</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -15813,7 +15817,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15846,7 +15850,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>smarters pro tv</t>
+          <t>smarters player pro</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -15887,7 +15891,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>smarters tv pro</t>
+          <t>smarters player tv</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -15928,7 +15932,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>smarterstv</t>
+          <t>smarters pro lite</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -15969,7 +15973,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>tv smarters</t>
+          <t>smarters pro tv</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -16010,7 +16014,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>tv smarters pro</t>
+          <t>smarters tv pro</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -16051,7 +16055,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>webos iptv</t>
+          <t>smarterstv</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -16059,7 +16063,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16092,11 +16096,11 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ip tv smarters pro</t>
+          <t>tv smarters</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -16105,7 +16109,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro/</t>
+          <t>/iptv-smarters-pro-samsung-lg/</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16123,11 +16127,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -16137,11 +16137,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ip tv smart</t>
+          <t>tv smarters pro</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro/</t>
+          <t>/iptv-smarters-pro-samsung-lg/</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -16178,20 +16178,20 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>iptv smarters</t>
+          <t>webos iptv</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>/iptv-smarters-pro/</t>
+          <t>/iptv-smarters-pro-samsung-lg/</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -16219,11 +16219,11 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>smarters pro</t>
+          <t>ip tv smarters pro</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -16250,7 +16250,11 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I376" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -16260,7 +16264,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>smarterspro</t>
+          <t>ip tv smart</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -16301,11 +16305,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>iptv smarter</t>
+          <t>iptv smarters</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -16342,11 +16346,11 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ip tv smart pro</t>
+          <t>smarters pro</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -16383,11 +16387,11 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ip tv smarter pro</t>
+          <t>smarterspro</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -16424,11 +16428,11 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ip tv smarters</t>
+          <t>iptv smarter</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -16465,7 +16469,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>iptv smart pro</t>
+          <t>ip tv smart pro</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -16506,7 +16510,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>iptv smarter pro</t>
+          <t>ip tv smarter pro</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -16547,7 +16551,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>iptv smarters lite</t>
+          <t>ip tv smarters</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -16588,7 +16592,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>iptv smarters player</t>
+          <t>iptv smart pro</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -16629,7 +16633,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>iptv smasters pro subscription</t>
+          <t>iptv smarter pro</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -16663,14 +16667,14 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>smarters player</t>
+          <t>iptv smarters lite</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -16711,11 +16715,11 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>iptv smarters pro</t>
+          <t>iptv smarters player</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -16752,15 +16756,15 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>iptv smarter pro downloader</t>
+          <t>iptv smasters pro subscription</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -16793,15 +16797,15 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>iptv smasters pro iphone</t>
+          <t>smarters player</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -16827,22 +16831,22 @@
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>iptv smasters roku</t>
+          <t>iptv smarters pro</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -16868,14 +16872,14 @@
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>declared by page</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>iptv smasters roku tv</t>
+          <t>iptv smarter pro downloader</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -16916,7 +16920,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>iptv smasters subscription</t>
+          <t>iptv smasters pro iphone</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -16924,7 +16928,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -16957,7 +16961,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>iptvsmarterspro</t>
+          <t>iptv smasters roku</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -16965,7 +16969,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -16991,14 +16995,14 @@
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>smart pro iptv</t>
+          <t>iptv smasters roku tv</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -17006,7 +17010,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -17032,14 +17036,14 @@
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>smarters tv</t>
+          <t>iptv smasters subscription</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -17080,11 +17084,11 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>best iptv for sports</t>
+          <t>iptvsmarterspro</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -17093,17 +17097,17 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>/iptv-sports/</t>
+          <t>/iptv-smarters-pro/</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>C informational (sports)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -17111,11 +17115,7 @@
           <t>en-CA</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -17125,11 +17125,11 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>iptv sport</t>
+          <t>smart pro iptv</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -17138,17 +17138,17 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>/iptv-sports/</t>
+          <t>/iptv-smarters-pro/</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>C informational (sports)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -17166,7 +17166,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>sportz iptv</t>
+          <t>smarters tv</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -17179,17 +17179,17 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>/iptv-sports/</t>
+          <t>/iptv-smarters-pro/</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>C informational (sports)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -17200,14 +17200,14 @@
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
-          <t>declared by page</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>iptv apple tv</t>
+          <t>best iptv for sports</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -17220,22 +17220,22 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>/iptv-sur-apple-tv-iphone/</t>
+          <t>/iptv-sports/</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>C informational (sports)</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -17252,35 +17252,35 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>iplaytv apple tv</t>
+          <t>iptv sport</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>/iptv-sur-apple-tv-iphone/</t>
+          <t>/iptv-sports/</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>C informational (sports)</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H401" t="inlineStr"/>
@@ -17293,7 +17293,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>iptv apple</t>
+          <t>sportz iptv</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -17301,27 +17301,27 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>/iptv-sur-apple-tv-iphone/</t>
+          <t>/iptv-sports/</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>C informational (sports)</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="H402" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>iptv chromecast</t>
+          <t>iptv apple</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -17365,7 +17365,11 @@
           <t>fr-CA</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I403" t="inlineStr">
         <is>
           <t>declared by page</t>
@@ -36386,7 +36390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -37775,17 +37779,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>/iptv-price/</t>
+          <t>/iptv-roku/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C informational / guide</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -37795,35 +37799,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>cheap iptv</t>
+          <t>iptv on roku tv</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>IPTV Price in Canada 2026: Plans From $9 | IPTVMaple</t>
+          <t>Can You Watch IPTV on Roku? Options for 2026 | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>/iptv-roku/</t>
+          <t>/iptv-price/</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -37833,18 +37837,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>iptv on roku tv</t>
+          <t>cheap iptv</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Can You Watch IPTV on Roku? Options for 2026 | IPTVMaple</t>
+          <t>IPTV Price in Canada 2026: Plans From $9 | IPTVMaple</t>
         </is>
       </c>
     </row>
@@ -38307,22 +38311,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>/iptv-sur-apple-tv-iphone/</t>
+          <t>/iptv-apple-tv/</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -38331,14 +38335,14 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>IPTV sur Apple TV et iPhone : guide d’installation | IPTVMaple</t>
+          <t>How to Watch IPTV on Apple TV 4K (2026 Guide) | IPTVMaple</t>
         </is>
       </c>
     </row>
@@ -38459,7 +38463,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>/plex-iptv/</t>
+          <t>/iplaytv/</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -38479,7 +38483,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>plex iptv</t>
+          <t>iplaytv</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -38490,14 +38494,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>IPTV on Plex: Can Plex Play M3U Live TV? (2026) | IPTVMaple</t>
+          <t>iPlayTV for Apple TV &amp; iPhone: IPTV Setup | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>/smartone-iptv/</t>
+          <t>/plex-iptv/</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -38517,7 +38521,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>smartone iptv</t>
+          <t>plex iptv</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -38528,72 +38532,72 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SmartOne IPTV Setup on Samsung, LG &amp; Android | IPTVMaple</t>
+          <t>IPTV on Plex: Can Plex Play M3U Live TV? (2026) | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>/abonnement-iptv/</t>
+          <t>/smartone-iptv/</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>abonnementiptv</t>
+          <t>smartone iptv</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Abonnement IPTV : 1, 6 ou 12 mois dès 9 $ | IPTVMaple</t>
+          <t>SmartOne IPTV Setup on Samsung, LG &amp; Android | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>/iplaytv/</t>
+          <t>/abonnement-iptv/</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>iplaytv</t>
+          <t>abonnementiptv</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -38604,7 +38608,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>iPlayTV for Apple TV &amp; iPhone: IPTV Setup | IPTVMaple</t>
+          <t>Abonnement IPTV : 1, 6 ou 12 mois dès 9 $ | IPTVMaple</t>
         </is>
       </c>
     </row>
@@ -38877,17 +38881,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>/iptv-guides/</t>
+          <t>/iptv-chromecast/</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>hub</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Guides &amp; trust</t>
+          <t>Devices &amp; hardware</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -38897,73 +38901,73 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>iptv for beginners</t>
+          <t>chromecast iptv</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IPTV Guides for Canada: Prices, Providers &amp; Setup | IPTVMaple</t>
+          <t>IPTV on Chromecast &amp; Google TV Streamer | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>/iptv-chromecast/</t>
+          <t>/iptv-sur-apple-tv-iphone/</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>chromecast iptv</t>
+          <t>iptv apple</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>IPTV on Chromecast &amp; Google TV Streamer | IPTVMaple</t>
+          <t>IPTV sur Apple TV et iPhone : guide d’installation | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>/iptv-apple-tv/</t>
+          <t>/iptv-guides/</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>hub</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Devices &amp; hardware</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -38973,18 +38977,18 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>iptv apple tv 4k</t>
+          <t>iptv for beginners</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>How to Watch IPTV on Apple TV 4K (2026 Guide) | IPTVMaple</t>
+          <t>IPTV Guides for Canada: Prices, Providers &amp; Setup | IPTVMaple</t>
         </is>
       </c>
     </row>
@@ -39257,27 +39261,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>/iptv-sur-smart-tv/</t>
+          <t>/iptv-lifetime/</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C informational (fr-CA)</t>
+          <t>C informational / guide</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Québec / French (fr-CA)</t>
+          <t>Guides &amp; trust</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>en-CA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>iptv ps5</t>
+          <t>iptv lifetime</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -39288,14 +39292,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>IPTV sur Smart TV, Fire Stick et PC : guide 2026 | IPTVMaple</t>
+          <t>Lifetime IPTV Subscription: Is It Worth It? | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>/iptv-quebec/</t>
+          <t>/iptv-sur-smart-tv/</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -39315,45 +39319,45 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>canal iptv</t>
+          <t>iptv ps5</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>IPTV Québec : chaînes québécoises en 4K dès 9 $ | IPTVMaple</t>
+          <t>IPTV sur Smart TV, Fire Stick et PC : guide 2026 | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>/romanian-iptv/</t>
+          <t>/iptv-quebec/</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>F community</t>
+          <t>C informational (fr-CA)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>International communities</t>
+          <t>Québec / French (fr-CA)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>en-CA</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>canale romanesti iptv</t>
+          <t>canal iptv</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -39364,24 +39368,24 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Romanian IPTV in Canada: Canale Românești Live | IPTVMaple</t>
+          <t>IPTV Québec : chaînes québécoises en 4K dès 9 $ | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>/canada/british-columbia/delta/</t>
+          <t>/romanian-iptv/</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E geo landing</t>
+          <t>F community</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>International communities</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -39391,7 +39395,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>delta iptv</t>
+          <t>canale romanesti iptv</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -39402,24 +39406,24 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IPTV Delta, BC – Live TV &amp; Sports in 4K | IPTVMaple</t>
+          <t>Romanian IPTV in Canada: Canale Românești Live | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>/bein-sports-iptv/</t>
+          <t>/canada/british-columbia/delta/</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C informational (sports)</t>
+          <t>E geo landing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -39429,7 +39433,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>iptv bein sport</t>
+          <t>delta iptv</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -39440,14 +39444,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>beIN Sports IPTV in Canada: Channels &amp; Setup | IPTVMaple</t>
+          <t>IPTV Delta, BC – Live TV &amp; Sports in 4K | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>/espn-iptv/</t>
+          <t>/bein-sports-iptv/</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -39467,7 +39471,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>iptv espn</t>
+          <t>iptv bein sport</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -39478,14 +39482,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ESPN on IPTV in Canada: ESPN 4K, ESPN2 &amp; ESPN+ | IPTVMaple</t>
+          <t>beIN Sports IPTV in Canada: Channels &amp; Setup | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>/nba-iptv/</t>
+          <t>/espn-iptv/</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -39505,7 +39509,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>iptv nba</t>
+          <t>iptv espn</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -39516,24 +39520,24 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>NBA IPTV: Watch Raptors &amp; Every NBA Game in 4K | IPTVMaple</t>
+          <t>ESPN on IPTV in Canada: ESPN 4K, ESPN2 &amp; ESPN+ | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>/canada/quebec/montreal/</t>
+          <t>/nba-iptv/</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E geo landing</t>
+          <t>C informational (sports)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -39543,7 +39547,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>iptv rive nord</t>
+          <t>iptv nba</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -39554,14 +39558,14 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>IPTV Montreal, QC – Live TV &amp; Sports in 4K | IPTVMaple</t>
+          <t>NBA IPTV: Watch Raptors &amp; Every NBA Game in 4K | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>/usa/arizona/phoenix/</t>
+          <t>/canada/quebec/montreal/</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -39581,7 +39585,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>phoenix iptv</t>
+          <t>iptv rive nord</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -39592,24 +39596,24 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>IPTV Phoenix, AZ – Live TV, Sports &amp; 4K | IPTVMaple</t>
+          <t>IPTV Montreal, QC – Live TV &amp; Sports in 4K | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>/m3u-playlist/</t>
+          <t>/usa/arizona/phoenix/</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>G device / app guide</t>
+          <t>E geo landing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Apps &amp; players</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -39619,7 +39623,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>pluto tv m3u</t>
+          <t>phoenix iptv</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -39630,24 +39634,24 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>What Is an M3U Playlist? IPTV M3U Guide (2026) | IPTVMaple</t>
+          <t>IPTV Phoenix, AZ – Live TV, Sports &amp; 4K | IPTVMaple</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>/uk-iptv/</t>
+          <t>/m3u-playlist/</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>F community</t>
+          <t>G device / app guide</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>International communities</t>
+          <t>Apps &amp; players</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -39657,7 +39661,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ukiptv</t>
+          <t>pluto tv m3u</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -39667,6 +39671,44 @@
         <v>50</v>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>What Is an M3U Playlist? IPTV M3U Guide (2026) | IPTVMaple</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>/uk-iptv/</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>F community</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>International communities</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>en-CA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ukiptv</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>50</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>UK IPTV in Canada: BBC, ITV &amp; Sky Sports Live | IPTVMaple</t>
         </is>

--- a/docs/keyword-map.xlsx
+++ b/docs/keyword-map.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/d56f9b2b-Keyword_Canada.xlsx</t>
+          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/7d244209-Keyword_Canada.xlsx</t>
         </is>
       </c>
     </row>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Formuler Z11 Pro Max &amp; Z-Series IPTV Box Guide (2026) | IPTVMaple</t>
+          <t>Formuler Z-Series IPTV Box Guide (2026) | IPTVMaple</t>
         </is>
       </c>
     </row>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Best IPTV for Sports in Canada (2026): NHL, UFC, NBA | IPTVMaple</t>
+          <t>Best IPTV for Sports in Canada (2026): NHL, UFC | IPTVMaple</t>
         </is>
       </c>
     </row>

--- a/docs/keyword-map.xlsx
+++ b/docs/keyword-map.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/7d244209-Keyword_Canada.xlsx</t>
+          <t>/root/.claude/uploads/5a4562d9-198c-51ab-b817-8b92809dcb72/a64d36a5-Keyword_Canada.xlsx</t>
         </is>
       </c>
     </row>
